--- a/data/box_situaciones.xlsx
+++ b/data/box_situaciones.xlsx
@@ -447,7 +447,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>154</v>
+        <v>187</v>
       </c>
     </row>
     <row r="3">
@@ -457,7 +457,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>3038</v>
+        <v>3654</v>
       </c>
     </row>
     <row r="4">
@@ -467,7 +467,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2763</v>
+        <v>3428</v>
       </c>
     </row>
   </sheetData>

--- a/data/box_situaciones.xlsx
+++ b/data/box_situaciones.xlsx
@@ -447,7 +447,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>187</v>
+        <v>805</v>
       </c>
     </row>
     <row r="3">
@@ -457,7 +457,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>3654</v>
+        <v>8288</v>
       </c>
     </row>
     <row r="4">
@@ -467,7 +467,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3428</v>
+        <v>7909</v>
       </c>
     </row>
   </sheetData>

--- a/data/box_situaciones.xlsx
+++ b/data/box_situaciones.xlsx
@@ -447,7 +447,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>805</v>
+        <v>1871</v>
       </c>
     </row>
     <row r="3">
@@ -457,7 +457,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>8288</v>
+        <v>16572</v>
       </c>
     </row>
     <row r="4">
@@ -467,7 +467,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>7909</v>
+        <v>15371</v>
       </c>
     </row>
   </sheetData>

--- a/data/box_situaciones.xlsx
+++ b/data/box_situaciones.xlsx
@@ -447,7 +447,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1871</v>
+        <v>2778</v>
       </c>
     </row>
     <row r="3">
@@ -457,7 +457,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>16572</v>
+        <v>24171</v>
       </c>
     </row>
     <row r="4">
@@ -467,7 +467,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>15371</v>
+        <v>22304</v>
       </c>
     </row>
   </sheetData>

--- a/data/box_situaciones.xlsx
+++ b/data/box_situaciones.xlsx
@@ -447,7 +447,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2778</v>
+        <v>22304</v>
       </c>
     </row>
     <row r="3">
@@ -467,7 +467,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>22304</v>
+        <v>2778</v>
       </c>
     </row>
   </sheetData>

--- a/data/box_situaciones.xlsx
+++ b/data/box_situaciones.xlsx
@@ -447,7 +447,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>22304</v>
+        <v>22307</v>
       </c>
     </row>
     <row r="3">
@@ -457,7 +457,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>24171</v>
+        <v>24173</v>
       </c>
     </row>
     <row r="4">
@@ -467,7 +467,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2778</v>
+        <v>2779</v>
       </c>
     </row>
   </sheetData>

--- a/data/box_situaciones.xlsx
+++ b/data/box_situaciones.xlsx
@@ -447,7 +447,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>22307</v>
+        <v>26192</v>
       </c>
     </row>
     <row r="3">
@@ -457,7 +457,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>24173</v>
+        <v>27898</v>
       </c>
     </row>
     <row r="4">
@@ -467,7 +467,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2779</v>
+        <v>4241</v>
       </c>
     </row>
   </sheetData>

--- a/data/box_situaciones.xlsx
+++ b/data/box_situaciones.xlsx
@@ -447,7 +447,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>26192</v>
+        <v>10699</v>
       </c>
     </row>
     <row r="3">
@@ -457,7 +457,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>27898</v>
+        <v>11161</v>
       </c>
     </row>
     <row r="4">
@@ -467,7 +467,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4241</v>
+        <v>1287</v>
       </c>
     </row>
   </sheetData>

--- a/data/box_situaciones.xlsx
+++ b/data/box_situaciones.xlsx
@@ -447,7 +447,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>10699</v>
+        <v>26697</v>
       </c>
     </row>
     <row r="3">
@@ -457,7 +457,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>11161</v>
+        <v>28531</v>
       </c>
     </row>
     <row r="4">
@@ -467,7 +467,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1287</v>
+        <v>4493</v>
       </c>
     </row>
   </sheetData>

--- a/data/box_situaciones.xlsx
+++ b/data/box_situaciones.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B4"/>
+  <dimension ref="A1:B5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -447,7 +447,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>26697</v>
+        <v>27269</v>
       </c>
     </row>
     <row r="3">
@@ -457,7 +457,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>28531</v>
+        <v>28807</v>
       </c>
     </row>
     <row r="4">
@@ -467,7 +467,17 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4493</v>
+        <v>4567</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>tipo_sin_causal</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>538</v>
       </c>
     </row>
   </sheetData>
